--- a/data/raw/returns/CRPL.xlsx
+++ b/data/raw/returns/CRPL.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,12 +493,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23T04:08:28+00:00</t>
+          <t>2026-06-27T08:06:47+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>404-8658915-5283560</t>
+          <t>407-0982528-9641969</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -526,22 +526,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2365315</t>
+          <t>LPNBOM4N40559118</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -549,12 +549,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-20T20:39:30+00:00</t>
+          <t>2026-06-26T07:21:03+00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>407-8253577-4026766</t>
+          <t>408-3504713-4740339</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -582,22 +582,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>LPNBLR5O0273517</t>
+          <t>LPNDEL2R84946927</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -605,12 +605,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-19T14:28:12+00:00</t>
+          <t>2026-06-25T15:18:30+00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>403-4924615-6655564</t>
+          <t>404-3227635-4950734</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -638,35 +638,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LPNBLR5P6413110</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>LPNCCX1B5586344</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Please kindly request what I am missing</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-18T07:44:45+00:00</t>
+          <t>2026-06-25T12:34:06+00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>405-3380213-8001958</t>
+          <t>405-1456558-2256311</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -694,7 +698,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -704,29 +708,25 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LPNCCX1B4279166</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Device is not functioning properly</t>
-        </is>
-      </c>
+          <t>LPNDEL2R85484282</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-17T05:15:21+00:00</t>
+          <t>2026-06-24T03:22:56+00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>171-4992464-5657953</t>
+          <t>404-7899663-9141951</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -754,22 +754,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LPNBOM4N41976296</t>
+          <t>LPNBLR5O0618795</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -777,12 +777,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-13T03:54:07+00:00</t>
+          <t>2026-06-23T04:08:28+00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>171-9300875-7128349</t>
+          <t>404-8658915-5283560</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -810,22 +810,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LPNBOM4N41235981</t>
+          <t>LPNMAA4Z2365315</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -833,12 +833,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-12T10:53:05+00:00</t>
+          <t>2026-06-20T20:39:30+00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>402-3739363-1565944</t>
+          <t>407-8253577-4026766</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -866,39 +866,35 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>LPNBOM4N41877983</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>not working at all,no LED  light to show the charge</t>
-        </is>
-      </c>
+          <t>LPNBLR5O0273517</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-12T04:06:23+00:00</t>
+          <t>2026-06-19T14:28:12+00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>171-8670987-2601911</t>
+          <t>403-4924615-6655564</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -926,22 +922,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>LPNBOM4N41240394</t>
+          <t>LPNBLR5P6413110</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -949,12 +945,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-11T12:09:55+00:00</t>
+          <t>2026-06-18T07:44:45+00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>404-3971623-1641153</t>
+          <t>405-3380213-8001958</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -982,7 +978,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -992,29 +988,29 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>LPNBLR5P9330031</t>
+          <t>LPNCCX1B4279166</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Not useful</t>
+          <t>Device is not functioning properly</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-10T03:35:27+00:00</t>
+          <t>2026-06-17T05:15:21+00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>404-7151786-3813904</t>
+          <t>171-4992464-5657953</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1042,22 +1038,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>LPNBLR5P6721579</t>
+          <t>LPNBOM4N41976296</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1065,12 +1061,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-08T06:19:18+00:00</t>
+          <t>2026-06-13T03:54:07+00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>408-3932770-3977962</t>
+          <t>171-9300875-7128349</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1108,12 +1104,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>LPNBOM4N40911350</t>
+          <t>LPNBOM4N41235981</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1121,12 +1117,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-07T12:18:27+00:00</t>
+          <t>2026-06-12T10:53:05+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>405-3895737-6273127</t>
+          <t>402-3739363-1565944</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1154,35 +1150,39 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>LPNBLR5P6681819</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>LPNBOM4N41877983</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>not working at all,no LED  light to show the charge</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-07T08:25:42+00:00</t>
+          <t>2026-06-12T04:06:23+00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>405-7209127-2373940</t>
+          <t>171-8670987-2601911</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1220,29 +1220,25 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>LPNBOM4N41477070</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Not working properly</t>
-        </is>
-      </c>
+          <t>LPNBOM4N41240394</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-07T08:16:05+00:00</t>
+          <t>2026-06-11T12:09:55+00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>408-8902852-3265136</t>
+          <t>404-3971623-1641153</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1270,7 +1266,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1280,25 +1276,29 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>LPNBOM4N40867786</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>LPNBLR5P9330031</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Not useful</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-06T06:04:59+00:00</t>
+          <t>2026-06-10T03:35:27+00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>408-8074884-6173915</t>
+          <t>404-7151786-3813904</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1326,22 +1326,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LPNBOM4N37594738</t>
+          <t>LPNBLR5P6721579</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1349,12 +1349,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-05T03:55:24+00:00</t>
+          <t>2026-06-08T06:19:18+00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>407-3423692-4605908</t>
+          <t>408-3932770-3977962</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>LPNDEL2R69813434</t>
+          <t>LPNBOM4N40911350</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1405,12 +1405,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-04T22:17:14+00:00</t>
+          <t>2026-06-07T12:18:27+00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>405-8342737-1137957</t>
+          <t>405-3895737-6273127</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1443,17 +1443,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>LPNBLR5P6916063</t>
+          <t>LPNBLR5P6681819</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1461,12 +1461,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-04T04:45:34+00:00</t>
+          <t>2026-06-07T08:25:42+00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>406-2580640-9601160</t>
+          <t>405-7209127-2373940</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1509,24 +1509,24 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>LPNBOM4N40559118</t>
+          <t>LPNBOM4N41477070</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Performance not better</t>
+          <t>Not working properly</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-04T04:38:47+00:00</t>
+          <t>2026-06-07T08:16:05+00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>404-7160476-0159530</t>
+          <t>408-8902852-3265136</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1554,22 +1554,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>LPNDEL2R69909771</t>
+          <t>LPNBOM4N40867786</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1577,12 +1577,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-03T07:42:50+00:00</t>
+          <t>2026-06-06T06:04:59+00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>408-7033772-5201936</t>
+          <t>408-8074884-6173915</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1610,22 +1610,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>LPNDEL2R69854947</t>
+          <t>LPNBOM4N37594738</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1633,12 +1633,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-02T11:28:54+00:00</t>
+          <t>2026-06-05T03:55:24+00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>403-2112133-1233965</t>
+          <t>407-3423692-4605908</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>LPNBLR5P7556919</t>
+          <t>LPNDEL2R69813434</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1689,12 +1689,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-01T14:46:18+00:00</t>
+          <t>2026-06-04T22:17:14+00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>406-1444499-1875548</t>
+          <t>405-8342737-1137957</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1727,17 +1727,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>LPNBLR5P7353787</t>
+          <t>LPNBLR5P6916063</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1745,12 +1745,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-01T12:16:15+00:00</t>
+          <t>2026-06-04T04:45:34+00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>402-5521735-9317952</t>
+          <t>406-2580640-9601160</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1778,39 +1778,39 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>LPNDEL2R69538739</t>
+          <t>LPNBOM4N40559118</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>It doesn&amp;#39;t work</t>
+          <t>Performance not better</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-01T06:26:09+00:00</t>
+          <t>2026-06-04T04:38:47+00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>402-2027934-1405149</t>
+          <t>404-7160476-0159530</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1848,12 +1848,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>LPNBLR5P8193069</t>
+          <t>LPNDEL2R69909771</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1861,12 +1861,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-01T05:30:09+00:00</t>
+          <t>2026-06-03T07:42:50+00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>408-4829494-0165133</t>
+          <t>408-7033772-5201936</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>DAMAGED_BY_FC</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>LPNBLR5P8223398</t>
+          <t>LPNDEL2R69854947</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1917,12 +1917,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-31T12:47:37+00:00</t>
+          <t>2026-06-02T11:28:54+00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>408-3178206-4989113</t>
+          <t>403-2112133-1233965</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>LPNDEL2R69744820</t>
+          <t>LPNBLR5P7556919</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1973,12 +1973,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-31T04:56:04+00:00</t>
+          <t>2026-06-01T14:46:18+00:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>171-4538397-9520308</t>
+          <t>406-1444499-1875548</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>LPNBLR5P7936663</t>
+          <t>LPNBLR5P7353787</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -2029,12 +2029,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-28T10:03:08+00:00</t>
+          <t>2026-06-01T12:16:15+00:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>404-3663729-7337922</t>
+          <t>402-5521735-9317952</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2062,35 +2062,39 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>LPNBLR5P4680950</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
+          <t>LPNDEL2R69538739</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>It doesn&amp;#39;t work</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-25T16:19:59+00:00</t>
+          <t>2026-06-01T06:26:09+00:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>407-8006280-6426725</t>
+          <t>402-2027934-1405149</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2123,17 +2127,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>LPNBLR5P7797937</t>
+          <t>LPNBLR5P8193069</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2141,12 +2145,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-25T12:46:33+00:00</t>
+          <t>2026-06-01T05:30:09+00:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>406-8222777-6229119</t>
+          <t>408-4829494-0165133</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2174,39 +2178,35 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>DAMAGED_BY_FC</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>LPNBOM4N37590319</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Stitching is not perfect work</t>
-        </is>
-      </c>
+          <t>LPNBLR5P8223398</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-17T07:21:17+00:00</t>
+          <t>2026-05-31T12:47:37+00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>402-4001896-2034744</t>
+          <t>408-3178206-4989113</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>LPNBLR5P5716205</t>
+          <t>LPNDEL2R69744820</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2257,12 +2257,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-15T05:28:36+00:00</t>
+          <t>2026-05-31T04:56:04+00:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>403-1142690-7087550</t>
+          <t>171-4538397-9520308</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2305,24 +2305,20 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>LPNBOM4N39742687</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>It’s difficult to load and sew for me. Also am not sure but the small thing that holds the bobbin seems to be missing. Big one for big spool is available.</t>
-        </is>
-      </c>
+          <t>LPNBLR5P7936663</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-13T14:07:55+00:00</t>
+          <t>2026-05-28T10:03:08+00:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>404-0375199-5259562</t>
+          <t>404-3663729-7337922</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2355,17 +2351,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>LPNBLR5P6433215</t>
+          <t>LPNBLR5P4680950</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2373,12 +2369,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-12T08:02:11+00:00</t>
+          <t>2026-05-25T16:19:59+00:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>403-3091421-6943540</t>
+          <t>407-8006280-6426725</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2406,22 +2402,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>LPNDEL2R83892100</t>
+          <t>LPNBLR5P7797937</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2429,12 +2425,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-10T17:31:26+00:00</t>
+          <t>2026-05-25T12:46:33+00:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>408-6829662-3833112</t>
+          <t>406-8222777-6229119</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2462,7 +2458,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2472,29 +2468,29 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>LPNBLR5P4444180</t>
+          <t>LPNBOM4N37590319</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Not working properly</t>
+          <t>Stitching is not perfect work</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-10T10:36:00+00:00</t>
+          <t>2026-05-17T07:21:17+00:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>408-5681274-3819529</t>
+          <t>402-4001896-2034744</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2522,7 +2518,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2537,7 +2533,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>LPNDEL2R82829895</t>
+          <t>LPNBLR5P5716205</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2545,12 +2541,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-10T09:36:24+00:00</t>
+          <t>2026-05-15T05:28:36+00:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>402-2604777-6654719</t>
+          <t>403-1142690-7087550</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2578,12 +2574,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2593,20 +2589,24 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>LPNDEL2R83108297</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
+          <t>LPNBOM4N39742687</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>It’s difficult to load and sew for me. Also am not sure but the small thing that holds the bobbin seems to be missing. Big one for big spool is available.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-08T09:41:46+00:00</t>
+          <t>2026-05-13T14:07:55+00:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>407-0316979-7690711</t>
+          <t>404-0375199-5259562</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2649,24 +2649,20 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>LPNDEL2R82591288</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Achcha nahi hai</t>
-        </is>
-      </c>
+          <t>LPNBLR5P6433215</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-04T10:08:17+00:00</t>
+          <t>2026-05-12T08:02:11+00:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>405-4137464-4742730</t>
+          <t>403-3091421-6943540</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2704,12 +2700,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>LPNDEL2R83764773</t>
+          <t>LPNDEL2R83892100</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2717,12 +2713,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-03T12:35:19+00:00</t>
+          <t>2026-05-10T17:31:26+00:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>404-5150861-3069912</t>
+          <t>408-6829662-3833112</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2750,39 +2746,39 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>LPNDEL2R83488686</t>
+          <t>LPNBLR5P4444180</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>This is my second piece... And still nt working with wired... Very bad false marketing... They say it works with wired but it&amp;#39;s not</t>
+          <t>Not working properly</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-03T11:29:03+00:00</t>
+          <t>2026-05-10T10:36:00+00:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>404-3570142-1994768</t>
+          <t>408-5681274-3819529</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2810,39 +2806,35 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>LPNBLR5P5411476</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Item not working</t>
-        </is>
-      </c>
+          <t>LPNDEL2R82829895</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-02T08:21:20+00:00</t>
+          <t>2026-05-10T09:36:24+00:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>403-4430191-2213903</t>
+          <t>402-2604777-6654719</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2870,39 +2862,35 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>LPNBOM4N37691234</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>It is not sewing</t>
-        </is>
-      </c>
+          <t>LPNDEL2R83108297</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-30T20:30:51+00:00</t>
+          <t>2026-05-08T09:41:46+00:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>405-5100838-1129110</t>
+          <t>407-0316979-7690711</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2930,35 +2918,39 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>LPNBLR5P4365378</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
+          <t>LPNDEL2R82591288</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Achcha nahi hai</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-30T08:57:15+00:00</t>
+          <t>2026-05-04T10:08:17+00:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>407-2743657-8027544</t>
+          <t>405-4137464-4742730</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2986,7 +2978,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2996,12 +2988,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>LPNBOM4N39059546</t>
+          <t>LPNDEL2R83764773</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -3009,12 +3001,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-30T04:05:06+00:00</t>
+          <t>2026-05-03T12:35:19+00:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>171-0309265-6717104</t>
+          <t>404-5150861-3069912</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3042,35 +3034,39 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>LPNBLR5P4172347</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+          <t>LPNDEL2R83488686</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>This is my second piece... And still nt working with wired... Very bad false marketing... They say it works with wired but it&amp;#39;s not</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-30T03:12:25+00:00</t>
+          <t>2026-05-03T11:29:03+00:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>402-7730485-6288354</t>
+          <t>404-3570142-1994768</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3103,30 +3099,34 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>LPNBLR5P3227374</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
+          <t>LPNBLR5P5411476</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Item not working</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-29T07:42:59+00:00</t>
+          <t>2026-05-02T08:21:20+00:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>407-1243239-3994721</t>
+          <t>403-4430191-2213903</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3164,29 +3164,29 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>NOT_AS_DESCRIBED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>LPNBLR5P4202600</t>
+          <t>LPNBOM4N37691234</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>It doesn&amp;#39;t work with type c regular mobile charger at all. After lot of struggle brought some other tried about after stitch with a single tread pulled all the threading just comes off. Defective piec</t>
+          <t>It is not sewing</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-29T04:40:28+00:00</t>
+          <t>2026-04-30T20:30:51+00:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>404-0443217-9168322</t>
+          <t>405-5100838-1129110</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3224,12 +3224,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>LPNBOM4N37986339</t>
+          <t>LPNBLR5P4365378</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -3237,12 +3237,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-28T07:45:01+00:00</t>
+          <t>2026-04-30T08:57:15+00:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>404-8788808-9675508</t>
+          <t>407-2743657-8027544</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>LPNDEL2R83046917</t>
+          <t>LPNBOM4N39059546</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3293,12 +3293,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-26T08:29:40+00:00</t>
+          <t>2026-04-30T04:05:06+00:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>402-0280256-7525143</t>
+          <t>171-0309265-6717104</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>LPNBLR5P4720547</t>
+          <t>LPNBLR5P4172347</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3349,12 +3349,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-25T12:37:01+00:00</t>
+          <t>2026-04-30T03:12:25+00:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>407-2393346-3028350</t>
+          <t>402-7730485-6288354</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3387,34 +3387,30 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>LPNBLR5P4203099</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Bobins and bobin stic are missing</t>
-        </is>
-      </c>
+          <t>LPNBLR5P3227374</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-23T04:07:08+00:00</t>
+          <t>2026-04-29T07:42:59+00:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>404-3023513-6645944</t>
+          <t>407-1243239-3994721</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3442,7 +3438,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3452,29 +3448,29 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>NOT_AS_DESCRIBED</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>LPNBOM4N39111315</t>
+          <t>LPNBLR5P4202600</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>needle control wheel missing</t>
+          <t>It doesn&amp;#39;t work with type c regular mobile charger at all. After lot of struggle brought some other tried about after stitch with a single tread pulled all the threading just comes off. Defective piec</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-23T03:57:00+00:00</t>
+          <t>2026-04-29T04:40:28+00:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>405-5707695-5426759</t>
+          <t>404-0443217-9168322</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3502,59 +3498,55 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>LPNCCX1B1495620</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Not working properly</t>
-        </is>
-      </c>
+          <t>LPNBOM4N37986339</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-22T10:50:32+00:00</t>
+          <t>2026-04-28T07:45:01+00:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>171-7269644-6636324</t>
+          <t>404-8788808-9675508</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FBA77111</t>
+          <t>FBA79349</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>B08CVP2HXP</t>
+          <t>B0D9KDQCCM</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>X0026A2H0L</t>
+          <t>X0028X0MRL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TONOR USB Microphone, Condenser Computer PC Mic with Tripod Stand, Metal,Pop Filter, Shock Mount for Gaming,Streaming,Podcasting,YouTube, Voice Over,Skype, Twitch,Compatible with Laptop Desktop, TC30</t>
+          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -3577,7 +3569,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>LPNDEL2R79145149</t>
+          <t>LPNDEL2R83046917</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -3585,12 +3577,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-04-19T21:28:00+00:00</t>
+          <t>2026-04-26T08:29:40+00:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>407-2474868-1439513</t>
+          <t>402-0280256-7525143</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3623,7 +3615,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3633,24 +3625,20 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>LPNBLR5P1924081</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Quality issue</t>
-        </is>
-      </c>
+          <t>LPNBLR5P4720547</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-04-19T04:31:34+00:00</t>
+          <t>2026-04-25T12:37:01+00:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>405-5788291-5039502</t>
+          <t>407-2393346-3028350</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3678,35 +3666,39 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>LPNCCX1B1329941</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
+          <t>LPNBLR5P4203099</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Bobins and bobin stic are missing</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-04-18T05:56:09+00:00</t>
+          <t>2026-04-23T04:07:08+00:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>402-8432744-9863527</t>
+          <t>404-3023513-6645944</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3734,55 +3726,59 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>LPNBLR5P1684050</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
+          <t>LPNBOM4N39111315</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>needle control wheel missing</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-04-17T16:25:54+00:00</t>
+          <t>2026-04-23T03:57:00+00:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>406-5535649-9235557</t>
+          <t>405-5707695-5426759</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBA79349</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D9KDQCCM</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>X0026I97S3</t>
+          <t>X0028X0MRL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NexLev Mattress, Sofa &amp; Carpet Vacuum Cleaner | For Dust Mites, Allergens &amp; Pet Hair | 4 Step Cleansing with Double Beat, UV Light, Dehumidification &amp; Vacuum | HEPA captures 99.99% Dust|MR-01</t>
+          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -3790,7 +3786,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3800,45 +3796,49 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>LPNBLR5R0690438</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
+          <t>LPNCCX1B1495620</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Not working properly</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-04-16T08:08:28+00:00</t>
+          <t>2026-04-22T10:50:32+00:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>403-6151321-2297166</t>
+          <t>171-7269644-6636324</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FBA79349</t>
+          <t>FBA77111</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>B0D9KDQCCM</t>
+          <t>B08CVP2HXP</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>X0028X0MRL</t>
+          <t>X0026A2H0L</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
+          <t>TONOR USB Microphone, Condenser Computer PC Mic with Tripod Stand, Metal,Pop Filter, Shock Mount for Gaming,Streaming,Podcasting,YouTube, Voice Over,Skype, Twitch,Compatible with Laptop Desktop, TC30</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>LPNDEL2R83011644</t>
+          <t>LPNDEL2R79145149</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -3869,12 +3869,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-04-15T17:33:50+00:00</t>
+          <t>2026-04-19T21:28:00+00:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>404-4584991-2364323</t>
+          <t>407-2474868-1439513</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3907,30 +3907,34 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>LPNBLR5P1573587</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
+          <t>LPNBLR5P1924081</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Quality issue</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-04-11T13:49:04+00:00</t>
+          <t>2026-04-19T04:31:34+00:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>171-8497189-8000353</t>
+          <t>405-5788291-5039502</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3958,22 +3962,22 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>LPNBLR5P2291259</t>
+          <t>LPNCCX1B1329941</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -3981,12 +3985,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-04-11T03:13:03+00:00</t>
+          <t>2026-04-18T05:56:09+00:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>406-4109197-9760360</t>
+          <t>402-8432744-9863527</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4014,22 +4018,22 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>LPNBOM4N37926926</t>
+          <t>LPNBLR5P1684050</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -4037,58 +4041,338 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>2026-04-17T16:25:54+00:00</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>406-5535649-9235557</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>FBA79263</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>X0026I97S3</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>NexLev Mattress, Sofa &amp; Carpet Vacuum Cleaner | For Dust Mites, Allergens &amp; Pet Hair | 4 Step Cleansing with Double Beat, UV Light, Dehumidification &amp; Vacuum | HEPA captures 99.99% Dust|MR-01</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>BLR5</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>SELLABLE</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>UNDELIVERABLE_REFUSED</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>LPNBLR5R0690438</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-04-16T08:08:28+00:00</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>403-6151321-2297166</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>FBA79349</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>B0D9KDQCCM</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>X0028X0MRL</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>DEL2</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>CUSTOMER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>QUALITY_UNACCEPTABLE</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>LPNDEL2R83011644</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-04-15T17:33:50+00:00</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>404-4584991-2364323</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>FBA79349</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>B0D9KDQCCM</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>X0028X0MRL</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>BLR5</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>CUSTOMER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>NOT_COMPATIBLE</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>LPNBLR5P1573587</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-04-11T13:49:04+00:00</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>171-8497189-8000353</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>FBA79349</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>B0D9KDQCCM</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>X0028X0MRL</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>BLR5</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>SELLABLE</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>UNDELIVERABLE_REFUSED</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>LPNBLR5P2291259</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-04-11T03:13:03+00:00</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>406-4109197-9760360</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>FBA79349</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>B0D9KDQCCM</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>X0028X0MRL</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>BOM4</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>SELLABLE</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>UNDELIVERABLE_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>LPNBOM4N37926926</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>2026-04-10T07:42:46+00:00</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>402-4830802-5020346</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>1</v>
-      </c>
-      <c r="H64" t="inlineStr">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>FBA79349</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>B0D9KDQCCM</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>X0028X0MRL</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="inlineStr">
         <is>
           <t>DEL2</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>DEFECTIVE</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>DAMAGED_BY_FC</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>LPNDEL2R81422070</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>Slightly damaged and holder for attaching bob pin is not found</t>
         </is>

--- a/data/raw/returns/CRPL.xlsx
+++ b/data/raw/returns/CRPL.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>return-date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>order-id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>fnsku</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>product-name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>fulfillment-center-id</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>detailed-disposition</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>license-plate-number</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>customer-comments</t>
         </is>

--- a/data/raw/returns/CRPL.xlsx
+++ b/data/raw/returns/CRPL.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-27T08:06:47+00:00</t>
+          <t>2026-07-05T14:54:25+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>407-0982528-9641969</t>
+          <t>406-8129799-5681941</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -514,22 +514,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>LPNBOM4N40559118</t>
+          <t>LPNBLR5O0925759</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -537,12 +537,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26T07:21:03+00:00</t>
+          <t>2026-06-27T08:06:47+00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>408-3504713-4740339</t>
+          <t>407-0982528-9641969</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -580,12 +580,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>LPNDEL2R84946927</t>
+          <t>LPNBOM4N40559118</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -593,12 +593,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25T15:18:30+00:00</t>
+          <t>2026-06-26T07:21:03+00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>404-3227635-4950734</t>
+          <t>408-3504713-4740339</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,39 +626,35 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LPNCCX1B5586344</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Please kindly request what I am missing</t>
-        </is>
-      </c>
+          <t>LPNDEL2R84946927</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25T12:34:06+00:00</t>
+          <t>2026-06-25T15:18:30+00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>405-1456558-2256311</t>
+          <t>404-3227635-4950734</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -686,35 +682,39 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LPNDEL2R85484282</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>LPNCCX1B5586344</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Please kindly request what I am missing</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24T03:22:56+00:00</t>
+          <t>2026-06-25T12:34:06+00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>404-7899663-9141951</t>
+          <t>405-1456558-2256311</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -742,22 +742,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LPNBLR5O0618795</t>
+          <t>LPNDEL2R85484282</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -765,12 +765,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-23T04:08:28+00:00</t>
+          <t>2026-06-24T03:22:56+00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>404-8658915-5283560</t>
+          <t>404-7899663-9141951</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -798,22 +798,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>MAA4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LPNMAA4Z2365315</t>
+          <t>LPNBLR5O0618795</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -821,12 +821,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-20T20:39:30+00:00</t>
+          <t>2026-06-23T04:08:28+00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>407-8253577-4026766</t>
+          <t>404-8658915-5283560</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>MAA4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>UNDELIVERABLE_UNKNOWN</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>LPNBLR5O0273517</t>
+          <t>LPNMAA4Z2365315</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -877,12 +877,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-19T14:28:12+00:00</t>
+          <t>2026-06-20T20:39:30+00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>403-4924615-6655564</t>
+          <t>407-8253577-4026766</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>LPNBLR5P6413110</t>
+          <t>LPNBLR5O0273517</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -933,12 +933,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-18T07:44:45+00:00</t>
+          <t>2026-06-19T14:28:12+00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>405-3380213-8001958</t>
+          <t>403-4924615-6655564</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -976,29 +976,25 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>LPNCCX1B4279166</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Device is not functioning properly</t>
-        </is>
-      </c>
+          <t>LPNBLR5P6413110</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-17T05:15:21+00:00</t>
+          <t>2026-06-18T07:44:45+00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>171-4992464-5657953</t>
+          <t>405-3380213-8001958</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1026,7 +1022,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1036,25 +1032,29 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>LPNBOM4N41976296</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>LPNCCX1B4279166</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Device is not functioning properly</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-13T03:54:07+00:00</t>
+          <t>2026-06-17T05:15:21+00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>171-9300875-7128349</t>
+          <t>171-4992464-5657953</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1087,17 +1087,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>LPNBOM4N41235981</t>
+          <t>LPNBOM4N41976296</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1105,12 +1105,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-12T10:53:05+00:00</t>
+          <t>2026-06-13T03:54:07+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>402-3739363-1565944</t>
+          <t>171-9300875-7128349</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1143,34 +1143,30 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>CUSTOMER_DAMAGED</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>DEFECTIVE</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>DEFECTIVE</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>LPNBOM4N41877983</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>not working at all,no LED  light to show the charge</t>
-        </is>
-      </c>
+          <t>LPNBOM4N41235981</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-12T04:06:23+00:00</t>
+          <t>2026-06-12T10:53:05+00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>171-8670987-2601911</t>
+          <t>402-3739363-1565944</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1208,25 +1204,29 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SWITCHEROO</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>LPNBOM4N41240394</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>LPNBOM4N41877983</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>not working at all,no LED  light to show the charge</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-11T12:09:55+00:00</t>
+          <t>2026-06-12T04:06:23+00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>404-3971623-1641153</t>
+          <t>171-8670987-2601911</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1254,39 +1254,35 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>SWITCHEROO</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>LPNBLR5P9330031</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Not useful</t>
-        </is>
-      </c>
+          <t>LPNBOM4N41240394</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-10T03:35:27+00:00</t>
+          <t>2026-06-11T12:09:55+00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>404-7151786-3813904</t>
+          <t>404-3971623-1641153</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1319,30 +1315,34 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LPNBLR5P6721579</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>LPNBLR5P9330031</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Not useful</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06-08T06:19:18+00:00</t>
+          <t>2026-06-10T03:35:27+00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>408-3932770-3977962</t>
+          <t>404-7151786-3813904</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>LPNBOM4N40911350</t>
+          <t>LPNBLR5P6721579</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1393,12 +1393,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06-07T12:18:27+00:00</t>
+          <t>2026-06-08T06:19:18+00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>405-3895737-6273127</t>
+          <t>408-3932770-3977962</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>LPNBLR5P6681819</t>
+          <t>LPNBOM4N40911350</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1449,12 +1449,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06-07T08:25:42+00:00</t>
+          <t>2026-06-07T12:18:27+00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>405-7209127-2373940</t>
+          <t>405-3895737-6273127</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1497,24 +1497,20 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>LPNBOM4N41477070</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Not working properly</t>
-        </is>
-      </c>
+          <t>LPNBLR5P6681819</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06-07T08:16:05+00:00</t>
+          <t>2026-06-07T08:25:42+00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>408-8902852-3265136</t>
+          <t>405-7209127-2373940</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1547,30 +1543,34 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>LPNBOM4N40867786</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>LPNBOM4N41477070</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Not working properly</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06-06T06:04:59+00:00</t>
+          <t>2026-06-07T08:16:05+00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>408-8074884-6173915</t>
+          <t>408-8902852-3265136</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>LPNBOM4N37594738</t>
+          <t>LPNBOM4N40867786</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1621,12 +1621,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06-05T03:55:24+00:00</t>
+          <t>2026-06-06T06:04:59+00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>407-3423692-4605908</t>
+          <t>408-8074884-6173915</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1654,22 +1654,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>LPNDEL2R69813434</t>
+          <t>LPNBOM4N37594738</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1677,12 +1677,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06-04T22:17:14+00:00</t>
+          <t>2026-06-05T03:55:24+00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>405-8342737-1137957</t>
+          <t>407-3423692-4605908</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1710,22 +1710,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>LPNBLR5P6916063</t>
+          <t>LPNDEL2R69813434</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1733,12 +1733,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06-04T04:45:34+00:00</t>
+          <t>2026-06-04T22:17:14+00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>406-2580640-9601160</t>
+          <t>405-8342737-1137957</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1776,29 +1776,25 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>LPNBOM4N40559118</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Performance not better</t>
-        </is>
-      </c>
+          <t>LPNBLR5P6916063</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06-04T04:38:47+00:00</t>
+          <t>2026-06-04T04:45:34+00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>404-7160476-0159530</t>
+          <t>406-2580640-9601160</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1826,12 +1822,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1841,20 +1837,24 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>LPNDEL2R69909771</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>LPNBOM4N40559118</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Performance not better</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06-03T07:42:50+00:00</t>
+          <t>2026-06-04T04:38:47+00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>408-7033772-5201936</t>
+          <t>404-7160476-0159530</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>LPNDEL2R69854947</t>
+          <t>LPNDEL2R69909771</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1905,12 +1905,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06-02T11:28:54+00:00</t>
+          <t>2026-06-03T07:42:50+00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>403-2112133-1233965</t>
+          <t>408-7033772-5201936</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>LPNBLR5P7556919</t>
+          <t>LPNDEL2R69854947</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1961,12 +1961,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06-01T14:46:18+00:00</t>
+          <t>2026-06-02T11:28:54+00:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>406-1444499-1875548</t>
+          <t>403-2112133-1233965</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2004,12 +2004,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>LPNBLR5P7353787</t>
+          <t>LPNBLR5P7556919</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -2017,12 +2017,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06-01T12:16:15+00:00</t>
+          <t>2026-06-01T14:46:18+00:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>402-5521735-9317952</t>
+          <t>406-1444499-1875548</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2050,39 +2050,35 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>LPNDEL2R69538739</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>It doesn&amp;#39;t work</t>
-        </is>
-      </c>
+          <t>LPNBLR5P7353787</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06-01T06:26:09+00:00</t>
+          <t>2026-06-01T12:16:15+00:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>402-2027934-1405149</t>
+          <t>402-5521735-9317952</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2110,35 +2106,39 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>LPNBLR5P8193069</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
+          <t>LPNDEL2R69538739</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>It doesn&amp;#39;t work</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06-01T05:30:09+00:00</t>
+          <t>2026-06-01T06:26:09+00:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>408-4829494-0165133</t>
+          <t>402-2027934-1405149</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>DAMAGED_BY_FC</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>LPNBLR5P8223398</t>
+          <t>LPNBLR5P8193069</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2189,12 +2189,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-31T12:47:37+00:00</t>
+          <t>2026-06-01T05:30:09+00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>408-3178206-4989113</t>
+          <t>408-4829494-0165133</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DAMAGED_BY_FC</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>LPNDEL2R69744820</t>
+          <t>LPNBLR5P8223398</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2245,12 +2245,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-31T04:56:04+00:00</t>
+          <t>2026-05-31T12:47:37+00:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>171-4538397-9520308</t>
+          <t>408-3178206-4989113</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>LPNBLR5P7936663</t>
+          <t>LPNDEL2R69744820</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2301,12 +2301,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-28T10:03:08+00:00</t>
+          <t>2026-05-31T04:56:04+00:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>404-3663729-7337922</t>
+          <t>171-4538397-9520308</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2339,17 +2339,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>LPNBLR5P4680950</t>
+          <t>LPNBLR5P7936663</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2357,12 +2357,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-25T16:19:59+00:00</t>
+          <t>2026-05-28T10:03:08+00:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>407-8006280-6426725</t>
+          <t>404-3663729-7337922</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>LPNBLR5P7797937</t>
+          <t>LPNBLR5P4680950</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2413,12 +2413,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-25T12:46:33+00:00</t>
+          <t>2026-05-25T16:19:59+00:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>406-8222777-6229119</t>
+          <t>407-8006280-6426725</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2446,39 +2446,35 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>LPNBOM4N37590319</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Stitching is not perfect work</t>
-        </is>
-      </c>
+          <t>LPNBLR5P7797937</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-17T07:21:17+00:00</t>
+          <t>2026-05-25T12:46:33+00:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>402-4001896-2034744</t>
+          <t>406-8222777-6229119</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2506,35 +2502,39 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>LPNBLR5P5716205</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
+          <t>LPNBOM4N37590319</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Stitching is not perfect work</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-15T05:28:36+00:00</t>
+          <t>2026-05-17T07:21:17+00:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>403-1142690-7087550</t>
+          <t>402-4001896-2034744</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2562,39 +2562,35 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>LPNBOM4N39742687</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>It’s difficult to load and sew for me. Also am not sure but the small thing that holds the bobbin seems to be missing. Big one for big spool is available.</t>
-        </is>
-      </c>
+          <t>LPNBLR5P5716205</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-13T14:07:55+00:00</t>
+          <t>2026-05-15T05:28:36+00:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>404-0375199-5259562</t>
+          <t>403-1142690-7087550</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2622,12 +2618,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2637,20 +2633,24 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>LPNBLR5P6433215</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
+          <t>LPNBOM4N39742687</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>It’s difficult to load and sew for me. Also am not sure but the small thing that holds the bobbin seems to be missing. Big one for big spool is available.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-12T08:02:11+00:00</t>
+          <t>2026-05-13T14:07:55+00:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>403-3091421-6943540</t>
+          <t>404-0375199-5259562</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2688,12 +2688,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>LPNDEL2R83892100</t>
+          <t>LPNBLR5P6433215</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2701,12 +2701,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-10T17:31:26+00:00</t>
+          <t>2026-05-12T08:02:11+00:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>408-6829662-3833112</t>
+          <t>403-3091421-6943540</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2734,39 +2734,35 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>LPNBLR5P4444180</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Not working properly</t>
-        </is>
-      </c>
+          <t>LPNDEL2R83892100</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-10T10:36:00+00:00</t>
+          <t>2026-05-10T17:31:26+00:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>408-5681274-3819529</t>
+          <t>408-6829662-3833112</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2794,12 +2790,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2809,20 +2805,24 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>LPNDEL2R82829895</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
+          <t>LPNBLR5P4444180</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Not working properly</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-10T09:36:24+00:00</t>
+          <t>2026-05-10T10:36:00+00:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>402-2604777-6654719</t>
+          <t>408-5681274-3819529</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>LPNDEL2R83108297</t>
+          <t>LPNDEL2R82829895</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2873,12 +2873,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-08T09:41:46+00:00</t>
+          <t>2026-05-10T09:36:24+00:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>407-0316979-7690711</t>
+          <t>402-2604777-6654719</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2921,24 +2921,20 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>LPNDEL2R82591288</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Achcha nahi hai</t>
-        </is>
-      </c>
+          <t>LPNDEL2R83108297</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-04T10:08:17+00:00</t>
+          <t>2026-05-08T09:41:46+00:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>405-4137464-4742730</t>
+          <t>407-0316979-7690711</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2971,30 +2967,34 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>LPNDEL2R83764773</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
+          <t>LPNDEL2R82591288</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Achcha nahi hai</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-03T12:35:19+00:00</t>
+          <t>2026-05-04T10:08:17+00:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>404-5150861-3069912</t>
+          <t>405-4137464-4742730</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3027,34 +3027,30 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>LPNDEL2R83488686</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>This is my second piece... And still nt working with wired... Very bad false marketing... They say it works with wired but it&amp;#39;s not</t>
-        </is>
-      </c>
+          <t>LPNDEL2R83764773</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-03T11:29:03+00:00</t>
+          <t>2026-05-03T12:35:19+00:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>404-3570142-1994768</t>
+          <t>404-5150861-3069912</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3082,39 +3078,39 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
+          <t>SELLABLE</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
           <t>DEFECTIVE</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>DEFECTIVE</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>LPNBLR5P5411476</t>
+          <t>LPNDEL2R83488686</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Item not working</t>
+          <t>This is my second piece... And still nt working with wired... Very bad false marketing... They say it works with wired but it&amp;#39;s not</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-02T08:21:20+00:00</t>
+          <t>2026-05-03T11:29:03+00:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>403-4430191-2213903</t>
+          <t>404-3570142-1994768</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3142,7 +3138,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3157,24 +3153,24 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>LPNBOM4N37691234</t>
+          <t>LPNBLR5P5411476</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>It is not sewing</t>
+          <t>Item not working</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-30T20:30:51+00:00</t>
+          <t>2026-05-02T08:21:20+00:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>405-5100838-1129110</t>
+          <t>403-4430191-2213903</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3202,35 +3198,39 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>LPNBLR5P4365378</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
+          <t>LPNBOM4N37691234</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>It is not sewing</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-30T08:57:15+00:00</t>
+          <t>2026-04-30T20:30:51+00:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>407-2743657-8027544</t>
+          <t>405-5100838-1129110</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>LPNBOM4N39059546</t>
+          <t>LPNBLR5P4365378</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3281,12 +3281,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-30T04:05:06+00:00</t>
+          <t>2026-04-30T08:57:15+00:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>171-0309265-6717104</t>
+          <t>407-2743657-8027544</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>LPNBLR5P4172347</t>
+          <t>LPNBOM4N39059546</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3337,12 +3337,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-30T03:12:25+00:00</t>
+          <t>2026-04-30T04:05:06+00:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>402-7730485-6288354</t>
+          <t>171-0309265-6717104</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>LPNBLR5P3227374</t>
+          <t>LPNBLR5P4172347</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -3393,12 +3393,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-29T07:42:59+00:00</t>
+          <t>2026-04-30T03:12:25+00:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>407-1243239-3994721</t>
+          <t>402-7730485-6288354</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3431,34 +3431,30 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>NOT_AS_DESCRIBED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>LPNBLR5P4202600</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>It doesn&amp;#39;t work with type c regular mobile charger at all. After lot of struggle brought some other tried about after stitch with a single tread pulled all the threading just comes off. Defective piec</t>
-        </is>
-      </c>
+          <t>LPNBLR5P3227374</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-29T04:40:28+00:00</t>
+          <t>2026-04-29T07:42:59+00:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>404-0443217-9168322</t>
+          <t>407-1243239-3994721</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3486,35 +3482,39 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>NOT_AS_DESCRIBED</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>LPNBOM4N37986339</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
+          <t>LPNBLR5P4202600</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>It doesn&amp;#39;t work with type c regular mobile charger at all. After lot of struggle brought some other tried about after stitch with a single tread pulled all the threading just comes off. Defective piec</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-28T07:45:01+00:00</t>
+          <t>2026-04-29T04:40:28+00:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>404-8788808-9675508</t>
+          <t>404-0443217-9168322</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>LPNDEL2R83046917</t>
+          <t>LPNBOM4N37986339</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -3565,12 +3565,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-04-26T08:29:40+00:00</t>
+          <t>2026-04-28T07:45:01+00:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>402-0280256-7525143</t>
+          <t>404-8788808-9675508</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>LPNBLR5P4720547</t>
+          <t>LPNDEL2R83046917</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -3621,12 +3621,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-04-25T12:37:01+00:00</t>
+          <t>2026-04-26T08:29:40+00:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>407-2393346-3028350</t>
+          <t>402-0280256-7525143</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3659,34 +3659,30 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>MISSING_PARTS</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>LPNBLR5P4203099</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Bobins and bobin stic are missing</t>
-        </is>
-      </c>
+          <t>LPNBLR5P4720547</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-04-23T04:07:08+00:00</t>
+          <t>2026-04-25T12:37:01+00:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>404-3023513-6645944</t>
+          <t>407-2393346-3028350</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3714,7 +3710,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3729,24 +3725,24 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>LPNBOM4N39111315</t>
+          <t>LPNBLR5P4203099</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>needle control wheel missing</t>
+          <t>Bobins and bobin stic are missing</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-04-23T03:57:00+00:00</t>
+          <t>2026-04-23T04:07:08+00:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>405-5707695-5426759</t>
+          <t>404-3023513-6645944</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3774,59 +3770,59 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BOM4</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>MISSING_PARTS</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>LPNCCX1B1495620</t>
+          <t>LPNBOM4N39111315</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Not working properly</t>
+          <t>needle control wheel missing</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-04-22T10:50:32+00:00</t>
+          <t>2026-04-23T03:57:00+00:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>171-7269644-6636324</t>
+          <t>405-5707695-5426759</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FBA77111</t>
+          <t>FBA79349</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>B08CVP2HXP</t>
+          <t>B0D9KDQCCM</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>X0026A2H0L</t>
+          <t>X0028X0MRL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>TONOR USB Microphone, Condenser Computer PC Mic with Tripod Stand, Metal,Pop Filter, Shock Mount for Gaming,Streaming,Podcasting,YouTube, Voice Over,Skype, Twitch,Compatible with Laptop Desktop, TC30</t>
+          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -3834,55 +3830,59 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>DEFECTIVE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>LPNDEL2R79145149</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
+          <t>LPNCCX1B1495620</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Not working properly</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-04-19T21:28:00+00:00</t>
+          <t>2026-04-22T10:50:32+00:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>407-2474868-1439513</t>
+          <t>171-7269644-6636324</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FBA79349</t>
+          <t>FBA77111</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>B0D9KDQCCM</t>
+          <t>B08CVP2HXP</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>X0028X0MRL</t>
+          <t>X0026A2H0L</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
+          <t>TONOR USB Microphone, Condenser Computer PC Mic with Tripod Stand, Metal,Pop Filter, Shock Mount for Gaming,Streaming,Podcasting,YouTube, Voice Over,Skype, Twitch,Compatible with Laptop Desktop, TC30</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -3890,39 +3890,35 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>DEFECTIVE</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>LPNBLR5P1924081</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Quality issue</t>
-        </is>
-      </c>
+          <t>LPNDEL2R79145149</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-04-19T04:31:34+00:00</t>
+          <t>2026-04-19T21:28:00+00:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>405-5788291-5039502</t>
+          <t>407-2474868-1439513</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3950,12 +3946,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>CCX1</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3965,20 +3961,24 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>LPNCCX1B1329941</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
+          <t>LPNBLR5P1924081</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Quality issue</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-04-18T05:56:09+00:00</t>
+          <t>2026-04-19T04:31:34+00:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>402-8432744-9863527</t>
+          <t>405-5788291-5039502</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>CCX1</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>LPNBLR5P1684050</t>
+          <t>LPNCCX1B1329941</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -4029,32 +4029,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-04-17T16:25:54+00:00</t>
+          <t>2026-04-18T05:56:09+00:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>406-5535649-9235557</t>
+          <t>402-8432744-9863527</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FBA79263</t>
+          <t>FBA79349</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D9KDQCCM</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>X0026I97S3</t>
+          <t>X0028X0MRL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NexLev Mattress, Sofa &amp; Carpet Vacuum Cleaner | For Dust Mites, Allergens &amp; Pet Hair | 4 Step Cleansing with Double Beat, UV Light, Dehumidification &amp; Vacuum | HEPA captures 99.99% Dust|MR-01</t>
+          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -4067,17 +4067,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>LPNBLR5R0690438</t>
+          <t>LPNBLR5P1684050</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4085,32 +4085,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-04-16T08:08:28+00:00</t>
+          <t>2026-04-17T16:25:54+00:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>403-6151321-2297166</t>
+          <t>406-5535649-9235557</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FBA79349</t>
+          <t>FBA79263</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>B0D9KDQCCM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>X0028X0MRL</t>
+          <t>X0026I97S3</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
+          <t>NexLev Mattress, Sofa &amp; Carpet Vacuum Cleaner | For Dust Mites, Allergens &amp; Pet Hair | 4 Step Cleansing with Double Beat, UV Light, Dehumidification &amp; Vacuum | HEPA captures 99.99% Dust|MR-01</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -4118,22 +4118,22 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>DEL2</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>CUSTOMER_DAMAGED</t>
+          <t>SELLABLE</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>QUALITY_UNACCEPTABLE</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>LPNDEL2R83011644</t>
+          <t>LPNBLR5R0690438</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -4141,12 +4141,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-04-15T17:33:50+00:00</t>
+          <t>2026-04-16T08:08:28+00:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>404-4584991-2364323</t>
+          <t>403-6151321-2297166</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>BLR5</t>
+          <t>DEL2</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>NOT_COMPATIBLE</t>
+          <t>QUALITY_UNACCEPTABLE</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>LPNBLR5P1573587</t>
+          <t>LPNDEL2R83011644</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -4197,12 +4197,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-04-11T13:49:04+00:00</t>
+          <t>2026-04-15T17:33:50+00:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>171-8497189-8000353</t>
+          <t>404-4584991-2364323</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4235,17 +4235,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SELLABLE</t>
+          <t>CUSTOMER_DAMAGED</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_REFUSED</t>
+          <t>NOT_COMPATIBLE</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>LPNBLR5P2291259</t>
+          <t>LPNBLR5P1573587</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -4253,12 +4253,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-04-11T03:13:03+00:00</t>
+          <t>2026-04-11T13:49:04+00:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>406-4109197-9760360</t>
+          <t>171-8497189-8000353</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>BOM4</t>
+          <t>BLR5</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
+          <t>UNDELIVERABLE_REFUSED</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>LPNBOM4N37926926</t>
+          <t>LPNBLR5P2291259</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -4309,58 +4309,114 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>2026-04-11T03:13:03+00:00</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>406-4109197-9760360</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>FBA79349</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>B0D9KDQCCM</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>X0028X0MRL</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>BOM4</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>SELLABLE</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>UNDELIVERABLE_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>LPNBOM4N37926926</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>2026-04-10T07:42:46+00:00</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>402-4830802-5020346</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>FBA79349</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>B0D9KDQCCM</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>X0028X0MRL</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="inlineStr">
         <is>
           <t>DEL2</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>DEFECTIVE</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>DAMAGED_BY_FC</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>LPNDEL2R81422070</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>Slightly damaged and holder for attaching bob pin is not found</t>
         </is>

--- a/data/raw/returns/CRPL.xlsx
+++ b/data/raw/returns/CRPL.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,66 +425,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>return-date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>order-id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fnsku</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>product-name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>fulfillment-center-id</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>detailed-disposition</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>license-plate-number</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>customer-comments</t>
         </is>
@@ -4249,178 +4261,6 @@
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-04-11T13:49:04+00:00</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>171-8497189-8000353</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G68" t="n">
-        <v>1</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>BLR5</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>SELLABLE</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>UNDELIVERABLE_REFUSED</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>LPNBLR5P2291259</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-04-11T03:13:03+00:00</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>406-4109197-9760360</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>BOM4</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>SELLABLE</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>UNDELIVERABLE_UNKNOWN</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>LPNBOM4N37926926</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-04-10T07:42:46+00:00</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>402-4830802-5020346</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G70" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>DEL2</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>DEFECTIVE</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>DAMAGED_BY_FC</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>LPNDEL2R81422070</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Slightly damaged and holder for attaching bob pin is not found</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/raw/returns/CRPL.xlsx
+++ b/data/raw/returns/CRPL.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3910,346 +3910,6 @@
       </c>
       <c r="L61" t="inlineStr"/>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-04-19T21:28:00+00:00</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>407-2474868-1439513</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>BLR5</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>SELLABLE</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>QUALITY_UNACCEPTABLE</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>LPNBLR5P1924081</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>Quality issue</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-04-19T04:31:34+00:00</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>405-5788291-5039502</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>CCX1</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>CUSTOMER_DAMAGED</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>QUALITY_UNACCEPTABLE</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>LPNCCX1B1329941</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-04-18T05:56:09+00:00</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>402-8432744-9863527</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>1</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>BLR5</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>CUSTOMER_DAMAGED</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>QUALITY_UNACCEPTABLE</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>LPNBLR5P1684050</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-04-17T16:25:54+00:00</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>406-5535649-9235557</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>FBA79263</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>B0CYSLCRQS</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>X0026I97S3</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>NexLev Mattress, Sofa &amp; Carpet Vacuum Cleaner | For Dust Mites, Allergens &amp; Pet Hair | 4 Step Cleansing with Double Beat, UV Light, Dehumidification &amp; Vacuum | HEPA captures 99.99% Dust|MR-01</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>1</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>BLR5</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>SELLABLE</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>UNDELIVERABLE_REFUSED</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>LPNBLR5R0690438</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-04-16T08:08:28+00:00</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>403-6151321-2297166</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>DEL2</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>CUSTOMER_DAMAGED</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>QUALITY_UNACCEPTABLE</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>LPNDEL2R83011644</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-04-15T17:33:50+00:00</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>404-4584991-2364323</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>BLR5</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>CUSTOMER_DAMAGED</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>NOT_COMPATIBLE</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>LPNBLR5P1573587</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/raw/returns/CRPL.xlsx
+++ b/data/raw/returns/CRPL.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,62 +429,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>return-date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>order-id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>asin</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fnsku</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>product-name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>fulfillment-center-id</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>detailed-disposition</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>license-plate-number</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>customer-comments</t>
         </is>

--- a/data/raw/returns/CRPL.xlsx
+++ b/data/raw/returns/CRPL.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3562,62 +3562,6 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-04-29T04:40:28+00:00</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>404-0443217-9168322</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>1</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>BOM4</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>CUSTOMER_DAMAGED</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>DEFECTIVE</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>LPNBOM4N37986339</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/raw/returns/CRPL.xlsx
+++ b/data/raw/returns/CRPL.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3502,66 +3502,6 @@
       </c>
       <c r="L54" t="inlineStr"/>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-04-29T07:42:59+00:00</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>407-1243239-3994721</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>BLR5</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>DEFECTIVE</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>NOT_AS_DESCRIBED</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>LPNBLR5P4202600</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>It doesn&amp;#39;t work with type c regular mobile charger at all. After lot of struggle brought some other tried about after stitch with a single tread pulled all the threading just comes off. Defective piec</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/raw/returns/CRPL.xlsx
+++ b/data/raw/returns/CRPL.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,466 +3042,6 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-05-04T10:08:17+00:00</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>405-4137464-4742730</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>DEL2</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>CUSTOMER_DAMAGED</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>QUALITY_UNACCEPTABLE</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>LPNDEL2R83764773</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-05-03T12:35:19+00:00</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>404-5150861-3069912</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>DEL2</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>SELLABLE</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>DEFECTIVE</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>LPNDEL2R83488686</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>This is my second piece... And still nt working with wired... Very bad false marketing... They say it works with wired but it&amp;#39;s not</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-05-03T11:29:03+00:00</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>404-3570142-1994768</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>BLR5</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>DEFECTIVE</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>DEFECTIVE</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>LPNBLR5P5411476</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Item not working</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-05-02T08:21:20+00:00</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>403-4430191-2213903</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>BOM4</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>DEFECTIVE</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>DEFECTIVE</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>LPNBOM4N37691234</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>It is not sewing</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-04-30T20:30:51+00:00</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>405-5100838-1129110</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>BLR5</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>CUSTOMER_DAMAGED</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>QUALITY_UNACCEPTABLE</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>LPNBLR5P4365378</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-04-30T08:57:15+00:00</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>407-2743657-8027544</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>BOM4</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>CUSTOMER_DAMAGED</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>NOT_COMPATIBLE</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>LPNBOM4N39059546</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-04-30T04:05:06+00:00</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>171-0309265-6717104</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>BLR5</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>CUSTOMER_DAMAGED</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>QUALITY_UNACCEPTABLE</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>LPNBLR5P4172347</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-04-30T03:12:25+00:00</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>402-7730485-6288354</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>FBA79349</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>B0D9KDQCCM</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>X0028X0MRL</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Nexlev Portable Sewing Machine| 2 Speed Settings| Cordless| Battery operated| USB Type C cord for Plug-in| Quick Fix DIY|Portable &amp; Compact| for all Fabrics| 1 Year Warranty| White</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>BLR5</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>CUSTOMER_DAMAGED</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>QUALITY_UNACCEPTABLE</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>LPNBLR5P3227374</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
